--- a/MainTop/29.04.2026 Таня ВБ/print.xlsx
+++ b/MainTop/29.04.2026 Таня ВБ/print.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\29.04.2026 Таня ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890470E1-13CA-426B-9801-4EEECF3E8818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F32485-5494-4E72-9A5D-2B5D02509ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="406">
   <si>
     <t>Артикул</t>
   </si>
@@ -1201,25 +1201,7 @@
     <t>Термонаклейка Мишка велосипед</t>
   </si>
   <si>
-    <t>Термонаклейки Nike Adidas Reebok Vans Puma набор</t>
-  </si>
-  <si>
     <t>Термонаклейка Мишка стоит с скейтом</t>
-  </si>
-  <si>
-    <t>Футболка Единорог</t>
-  </si>
-  <si>
-    <t>Футболка Соник Ежик Sonic</t>
-  </si>
-  <si>
-    <t>Платье желтое</t>
-  </si>
-  <si>
-    <t>Футболка Человек паук Spiderman</t>
-  </si>
-  <si>
-    <t>Термонаклейка набор Щенячий Патруль Paw Patrol</t>
   </si>
   <si>
     <t>Термонаклейка Шредер и Кренг из Черепашек-ниндзя</t>
@@ -1671,7 +1653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F407"/>
+  <dimension ref="A1:F401"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -7934,7 +7916,7 @@
         <v>12</v>
       </c>
       <c r="F313">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -8554,7 +8536,7 @@
         <v>12</v>
       </c>
       <c r="F344">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -9134,7 +9116,7 @@
         <v>12</v>
       </c>
       <c r="F373">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -9274,7 +9256,7 @@
         <v>12</v>
       </c>
       <c r="F380">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -9294,7 +9276,7 @@
         <v>12</v>
       </c>
       <c r="F381">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -9314,7 +9296,7 @@
         <v>12</v>
       </c>
       <c r="F382">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -9394,7 +9376,7 @@
         <v>12</v>
       </c>
       <c r="F386">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -9414,7 +9396,7 @@
         <v>12</v>
       </c>
       <c r="F387">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -9434,7 +9416,7 @@
         <v>12</v>
       </c>
       <c r="F388">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -9445,7 +9427,7 @@
         <v>0</v>
       </c>
       <c r="C389">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D389">
         <v>0</v>
@@ -9454,7 +9436,7 @@
         <v>12</v>
       </c>
       <c r="F389">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -9465,7 +9447,7 @@
         <v>0</v>
       </c>
       <c r="C390">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D390">
         <v>0</v>
@@ -9474,7 +9456,7 @@
         <v>12</v>
       </c>
       <c r="F390">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -9485,7 +9467,7 @@
         <v>0</v>
       </c>
       <c r="C391">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D391">
         <v>0</v>
@@ -9505,7 +9487,7 @@
         <v>0</v>
       </c>
       <c r="C392">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D392">
         <v>0</v>
@@ -9514,7 +9496,7 @@
         <v>12</v>
       </c>
       <c r="F392">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -9525,7 +9507,7 @@
         <v>0</v>
       </c>
       <c r="C393">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D393">
         <v>0</v>
@@ -9534,7 +9516,7 @@
         <v>12</v>
       </c>
       <c r="F393">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -9545,7 +9527,7 @@
         <v>0</v>
       </c>
       <c r="C394">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D394">
         <v>0</v>
@@ -9565,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="C395">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D395">
         <v>0</v>
@@ -9574,7 +9556,7 @@
         <v>12</v>
       </c>
       <c r="F395">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -9585,7 +9567,7 @@
         <v>0</v>
       </c>
       <c r="C396">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D396">
         <v>0</v>
@@ -9594,7 +9576,7 @@
         <v>12</v>
       </c>
       <c r="F396">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -9605,7 +9587,7 @@
         <v>0</v>
       </c>
       <c r="C397">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D397">
         <v>0</v>
@@ -9614,7 +9596,7 @@
         <v>12</v>
       </c>
       <c r="F397">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -9625,7 +9607,7 @@
         <v>0</v>
       </c>
       <c r="C398">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D398">
         <v>0</v>
@@ -9634,7 +9616,7 @@
         <v>12</v>
       </c>
       <c r="F398">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -9645,7 +9627,7 @@
         <v>0</v>
       </c>
       <c r="C399">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D399">
         <v>0</v>
@@ -9685,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="C401">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D401">
         <v>0</v>
@@ -9694,126 +9676,6 @@
         <v>12</v>
       </c>
       <c r="F401">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A402" t="s">
-        <v>406</v>
-      </c>
-      <c r="B402">
-        <v>0</v>
-      </c>
-      <c r="C402">
-        <v>1</v>
-      </c>
-      <c r="D402">
-        <v>0</v>
-      </c>
-      <c r="E402">
-        <v>12</v>
-      </c>
-      <c r="F402">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A403" t="s">
-        <v>407</v>
-      </c>
-      <c r="B403">
-        <v>0</v>
-      </c>
-      <c r="C403">
-        <v>0</v>
-      </c>
-      <c r="D403">
-        <v>0</v>
-      </c>
-      <c r="E403">
-        <v>12</v>
-      </c>
-      <c r="F403">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A404" t="s">
-        <v>408</v>
-      </c>
-      <c r="B404">
-        <v>0</v>
-      </c>
-      <c r="C404">
-        <v>0</v>
-      </c>
-      <c r="D404">
-        <v>0</v>
-      </c>
-      <c r="E404">
-        <v>12</v>
-      </c>
-      <c r="F404">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A405" t="s">
-        <v>409</v>
-      </c>
-      <c r="B405">
-        <v>0</v>
-      </c>
-      <c r="C405">
-        <v>4</v>
-      </c>
-      <c r="D405">
-        <v>0</v>
-      </c>
-      <c r="E405">
-        <v>12</v>
-      </c>
-      <c r="F405">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A406" t="s">
-        <v>410</v>
-      </c>
-      <c r="B406">
-        <v>0</v>
-      </c>
-      <c r="C406">
-        <v>4</v>
-      </c>
-      <c r="D406">
-        <v>0</v>
-      </c>
-      <c r="E406">
-        <v>12</v>
-      </c>
-      <c r="F406">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A407" t="s">
-        <v>411</v>
-      </c>
-      <c r="B407">
-        <v>0</v>
-      </c>
-      <c r="C407">
-        <v>4</v>
-      </c>
-      <c r="D407">
-        <v>0</v>
-      </c>
-      <c r="E407">
-        <v>12</v>
-      </c>
-      <c r="F407">
         <v>0</v>
       </c>
     </row>
